--- a/test_code_creation_name/doc/RP2_10_結合テスト仕様書.xlsx
+++ b/test_code_creation_name/doc/RP2_10_結合テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eina-ichinari\git\lms-test-src-rp2\test_code_creation_name\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D18582-46E2-4168-A51C-7AA9812FEE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8F5740-6F4F-40A0-8194-046694CD9A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1725" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1725" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="181">
   <si>
     <t>関係者外秘</t>
   </si>
@@ -1239,6 +1239,14 @@
   <si>
     <t>利用規約同意画面・パスワード変更画面には遷移せず、コース詳細画面に遷移すること</t>
   </si>
+  <si>
+    <t>【ログイン画面】
+以下の入力値を入力し、「ログイン」ボタンを押下する。
+【入力値】（初回ログイン済み）
+ログインID：StudentAA01
+パスワード：StudentAA011</t>
+    <phoneticPr fontId="20"/>
+  </si>
 </sst>
 </file>
 
@@ -14814,14 +14822,14 @@
       <c r="BM5" s="33"/>
       <c r="BN5" s="33"/>
     </row>
-    <row r="6" spans="1:66" ht="65.849999999999994" customHeight="1">
+    <row r="6" spans="1:66" ht="76.5" customHeight="1">
       <c r="B6" s="26">
         <v>2</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>

--- a/test_code_creation_name/doc/RP2_10_結合テスト仕様書.xlsx
+++ b/test_code_creation_name/doc/RP2_10_結合テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eina-ichinari\git\lms-test-src-rp2\test_code_creation_name\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E44007-1BB3-466A-A563-27A71B3E77B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C38F83-7722-4210-8C2B-4F73D34DC0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16755" yWindow="4980" windowWidth="12495" windowHeight="11295" tabRatio="500" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="16" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="185">
   <si>
     <t>関係者外秘</t>
   </si>
@@ -608,41 +608,9 @@
     <t>勤怠情報直接変更画面に遷移すること</t>
   </si>
   <si>
-    <t>【勤怠情報直接変更画面】
-全ての研修日程の勤怠情報を以下の値で入力し、「更新」ボタンを押下する
-出勤：9:00
-退勤：18:00
-中抜け時間：1時間
-備考；テスト</t>
-  </si>
-  <si>
     <t xml:space="preserve">・勤怠管理画面に遷移すること
 ・入力された内容が反映されていること
 </t>
-  </si>
-  <si>
-    <t>【勤怠情報直接変更画面】
-以下の値を入力し、「更新」ボタンを押下する
-【入力値】
-出勤（時）：09
-出勤（分）：（空文字）
-退勤（時）：09
-退勤（分）：（空文字）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">勤怠情報直接変更画面に自画面遷移し、以下の入力チェックエラーメッセージが表示されること
-「出勤時間が正しく入力されていません。」
-「退勤時間が正しく入力されていません。」
-</t>
-  </si>
-  <si>
-    <t>【勤怠情報直接変更画面】
-以下の値を入力し、「更新」ボタンを押下する
-【入力値】
-出勤（時）：（空文字）
-出勤（分）：（空文字）
-退勤（時）：18
-退勤（分）：00</t>
   </si>
   <si>
     <t xml:space="preserve">勤怠情報直接変更画面に自画面遷移し、以下の入力チェックエラーメッセージが表示されること
@@ -650,98 +618,9 @@
 </t>
   </si>
   <si>
-    <t>【勤怠情報直接変更画面】
-以下の値を入力し、「更新」ボタンを押下する
-【入力値】
-出勤（時）：18
-出勤（分）：00
-退勤（時）：09
-退勤（分）：00</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">勤怠情報直接変更画面に自画面遷移し、以下の入力チェックエラーメッセージが表示されること
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>「退勤時刻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>[8]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>は出勤時刻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>[8]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">より後でなければいけません。」
-</t>
-    </r>
-  </si>
-  <si>
-    <t>【勤怠情報直接変更画面】
-以下の値を入力し、「更新」ボタンを押下する
-【入力値】
-出勤（時）：09
-出勤（分）：00
-退勤（時）：10
-退勤（分）：00
-中抜け時間：1時間15分</t>
-  </si>
-  <si>
     <t xml:space="preserve">勤怠情報直接変更画面に自画面遷移し、以下の入力チェックエラーメッセージが表示されること
 「中抜け時間が勤務時間を超えています。」
 </t>
-  </si>
-  <si>
-    <t>【勤怠情報直接変更画面】
-以下の値を入力し、「更新」ボタンを押下する
-【入力値】
-出勤（時）：09
-出勤（分）：00
-退勤（時）：10
-退勤（分）：00
-備考：
-0123456789abcdefghijklmnopqrstuvwxyz
-ABCDEFGHIJKLMNOPQRSTUVWXYZ１２３４５６７８９ａｂｃｄｅｆｇｈｉｊｋｌｍｎｏｐｑｒｓｔｕｖｗｘｙｚＡＢＣＤＥＦＧＨＩＪＫＬＭＮＯＰＱＲＳＴＵＶＷＸＹＺあいうえおかきくけこさしすせそたちつてとなにぬねのはひふへほまみむめもやゆよらりるれろわをんアイウエオカキクケコサシスセソタチツテトナニヌネノハヒフヘホマミムメモヤユヨラリルレロワヲン一二三四五六七八九十①②③④⑤⑥⑦⑧⑨⑩!-/:-@¥[-`{-~]*$</t>
   </si>
   <si>
     <t xml:space="preserve">勤怠情報直接変更画面に自画面遷移し、以下の入力チェックエラーメッセージが表示されること
@@ -790,32 +669,8 @@
     <t>試験開始画面に遷移後、当該試験の結果が反映されること</t>
   </si>
   <si>
-    <t xml:space="preserve">【試験問題画面】
-以下の値で入力し、「確認画面へ進む」ボタンを押下する
-第1問 3
-第2問 3
-第3問 1
-第4問 1
-第5問 2
-第6問 2
-第7問 1
-第8問 1
-第9問 1
-第10問 1 
-第11問 4
-第12問 1
-</t>
-  </si>
-  <si>
     <t>・試験回答確認画面に遷移すること
 ・入力した内容が反映されていること</t>
-  </si>
-  <si>
-    <t>【ログイン画面】
-以下の入力値を入力し、「ログイン」ボタンを押下する
-【入力値】
-ログインID：StudentAA02
-パスワード：StudentAA02</t>
   </si>
   <si>
     <t>・ログインに成功し、利用規約同意画面に遷移すること
@@ -859,80 +714,8 @@
 No.4で表示された「パスワード変更の確認」モーダルダイアログに対し、「変更」ボタンを押下する</t>
   </si>
   <si>
-    <t>パスワード変更画面に自画面遷移し
-以下の入力チェックエラーメッセージが表示されること
-現在のパスワード：現在のパスワードは必須です。
-新しいパスワード：「パスワード」には半角英数字のみ使用可能です。また、半角英大文字、半角英小文字、数字を含めた8～20文字を入力してください。
-パスワードは必須です。
-確認パスワード：確認パスワードは必須です。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【パスワード変更画面】
-以下の入力値を入力し、「変更」ボタンを押下する
-【入力値】
-現在のパスワード：No.2のパスワード
-新しいパスワード：Test
-確認パスワード：testtest
-</t>
-  </si>
-  <si>
     <t>【パスワード変更画面】
 No.7で表示された「パスワード変更の確認」モーダルダイアログに対し、「変更」ボタンを押下する</t>
-  </si>
-  <si>
-    <t>パスワード変更画面に自画面遷移し
-以下の入力チェックエラーメッセージが表示されること
-新しいパスワード：「パスワード」には半角英数字のみ使用可能です。また、半角英大文字、半角英小文字、数字を含めた8～20文字を入力してください。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【パスワード変更画面】
-以下の入力値を入力し、「変更」ボタンを押下する
-【入力値】
-現在のパスワード：No.2のパスワード
-新しいパスワード：0123456789abcdefghij(20文字)
-確認パスワード：testtest
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【パスワード変更画面】
-以下の入力値を入力し、「変更」ボタンを押下する
-【入力値】
-現在のパスワード：No.1のパスワード
-新しいパスワード：1111111111
-確認パスワード：testtest
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【パスワード変更画面】
-以下の入力値を入力し、「変更」ボタンを押下する
-【入力値】
-現在のパスワード：No.2のパスワード
-新しいパスワード：No.2のパスワード
-確認パスワード：testTest123
-</t>
-  </si>
-  <si>
-    <t>パスワード変更画面に自画面遷移し
-以下の入力チェックエラーメッセージが表示されること
-現在のパスワード：現在と同じパスワードは使用できません。
-新しいパスワード：現在と同じパスワードは使用できません。
-パスワードと確認パスワードが一致しません。</t>
-  </si>
-  <si>
-    <t>【ログイン画面】
-以下の入力値を入力し、「ログイン」ボタンを押下する。
-【入力値】
-ログインID：StudentAA03
-パスワード：StudentAA03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【パスワード変更画面】
-以下の入力値を入力し、「変更」ボタンを押下する
-【入力値】
-現在のパスワード：StudentAA03
-新しいパスワード：StudentAA03test
-確認パスワード：StudentAA03test
-</t>
   </si>
   <si>
     <t>コース詳細画面に遷移すること</t>
@@ -1371,6 +1154,253 @@
     </r>
     <phoneticPr fontId="20"/>
   </si>
+  <si>
+    <t xml:space="preserve">【コース詳細画面】
+「2022年10月2日(日)　アルゴリズム、フローチャート」が「試験有」であることを確認し、詳細ボタンを押下する
+</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【勤怠情報直接変更画面】
+全ての研修日程の勤怠情報を以下の値で入力し、「更新」ボタンを押下する
+出勤：9:00
+退勤：18:00
+</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>勤怠情報直接変更画面に遷移すること</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>【勤怠情報直接変更画面】
+以下の値を入力し、「更新」ボタンを押下する
+【入力値】
+出勤（時）：（空文字）
+出勤（分）：00
+退勤（時）：18
+退勤（分）：00</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t xml:space="preserve">勤怠情報直接変更画面に自画面遷移し、以下の入力チェックエラーメッセージが表示されること
+「出勤時間が正しく入力されていません。」
+</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>【勤怠情報直接変更画面】
+以下の値を入力し、「更新」ボタンを押下する
+【入力値】
+出勤（時）：（空文字）
+出勤（分）：（空文字）
+退勤（時）：18
+退勤（分）：00</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【試験問題画面】
+以下の値で入力し、「確認画面へ進む」ボタンを押下する
+第1問 3
+第2問 3
+第3問 1
+第4問 1
+第5問 2
+第6問 2
+第7問 1
+第8問 1
+第9問 1
+第10問 1 
+第11問 4
+第12問 1
+</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>【勤怠情報直接変更画面】
+以下の値を入力し、「更新」ボタンを押下する
+【入力値】
+出勤（時）：19
+出勤（分）：00
+退勤（時）：09
+退勤（分）：00</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">勤怠情報直接変更画面に自画面遷移し、以下の入力チェックエラーメッセージが表示されること
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「退勤時刻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>[0]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は出勤時刻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>[0]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">より後でなければいけません。」
+</t>
+    </r>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>【勤怠情報直接変更画面】
+以下の値を入力し、「更新」ボタンを押下する
+【入力値】
+出勤（時）：17
+出勤（分）：00
+退勤（時）：18
+退勤（分）：00
+中抜け時間：2時間</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>【勤怠情報直接変更画面】
+以下の値を入力し、「更新」ボタンを押下する
+【入力値】
+出勤（時）：09
+出勤（分）：00
+退勤（時）：18
+退勤（分）：00
+備考：
+0123456789abcdefghijklmnopqrstuvwxyz
+ABCDEFGHIJKLMNOPQRSTUVWXYZ１２３４５６７８９ａｂｃｄｅｆｇｈｉｊｋｌｍｎｏｐｑｒｓｔｕｖｗｘｙｚＡＢＣＤＥＦＧＨＩＪＫＬＭＮＯＰＱＲＳＴＵＶＷＸＹＺあいうえおかきくけこさしすせそたちつてとなにぬねのはひふへほまみむめもやゆよらりるれろわをんアイウエオカキクケコサシスセソタチツテトナニヌネノハヒフヘホマミムメモヤユヨラリルレロワヲン一二三四五六七八九十①②③④⑤⑥⑦⑧⑨⑩!-/:-@¥[-`{-~]*$</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t xml:space="preserve">試験結果画面に遷移すること
+</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>試験開始画面に遷移後、当該試験の結果が反映されること</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>【ログイン画面】
+以下の入力値を入力し、「ログイン」ボタンを押下する
+【入力値】
+ログインID：StudentAA03
+パスワード：StudentAA03</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>【ログイン画面】
+以下の入力値を入力し、「ログイン」ボタンを押下する
+【入力値】
+ログインID：StudentAA02
+パスワード：StudentAA02</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【パスワード変更画面】
+以下の入力値を入力し、「変更」ボタンを押下する
+【入力値】
+現在のパスワード：StudentAA03
+新しいパスワード：StudentAA03test
+確認パスワード：StudentAA03test
+</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>【ログイン画面】
+以下の入力値を入力し、「ログイン」ボタンを押下する。
+【入力値】
+ログインID：StudentAA03
+パスワード：StudentAA03</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>パスワード変更画面に自画面遷移し
+以下の入力チェックエラーメッセージが表示されること
+新しいパスワード：「パスワード」には半角英数字のみ使用可能です。また、半角英大文字、半角英小文字、数字を含めた8～20文字を入力してください。</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>「パスワード変更の確認」モーダルダイアログが表示されること</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>パスワード変更画面に自画面遷移し
+以下の入力チェックエラーメッセージが表示されること
+現在のパスワード：現在のパスワードは必須です。
+新しいパスワード：「パスワード」には半角英数字のみ使用可能です。また、半角英大文字、半角英小文字、数字を含めた8～20文字を入力してください。
+パスワードは必須です。
+確認パスワード：確認パスワードは必須です。</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【パスワード変更画面】
+以下の入力値を入力し、「変更」ボタンを押下する
+【入力値】
+現在のパスワード：No.2のパスワード
+新しいパスワード：0123abcdABCD!#$%0123(20文字)
+確認パスワード：0123abcdABCD!#$%0123(20文字)
+</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【パスワード変更画面】
+以下の入力値を入力し、「変更」ボタンを押下する
+【入力値】
+現在のパスワード：No.2のパスワード
+新しいパスワード：testtest
+確認パスワード：testtest
+</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【パスワード変更画面】
+以下の入力値を入力し、「変更」ボタンを押下する
+【入力値】
+現在のパスワード：No.1のパスワード
+新しいパスワード：testTest1234
+確認パスワード：testTest5678
+</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>パスワード変更画面に自画面遷移し
+以下の入力チェックエラーメッセージが表示されること
+新しいパスワード：パスワードと確認パスワードが一致しません。</t>
+    <phoneticPr fontId="20"/>
+  </si>
 </sst>
 </file>
 
@@ -1640,7 +1670,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1752,6 +1782,24 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2204,7 +2252,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="27" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -2277,7 +2325,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -2350,7 +2398,7 @@
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="31" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
@@ -2423,7 +2471,7 @@
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
       <c r="E8" s="31" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
@@ -2496,7 +2544,7 @@
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
       <c r="E9" s="31" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
@@ -3361,7 +3409,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="27" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -3434,7 +3482,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -3580,7 +3628,7 @@
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
       <c r="E8" s="31" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
@@ -3605,7 +3653,7 @@
       <c r="Z8" s="31"/>
       <c r="AA8" s="31"/>
       <c r="AB8" s="31" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="AC8" s="31"/>
       <c r="AD8" s="31"/>
@@ -3653,7 +3701,7 @@
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
       <c r="E9" s="31" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
@@ -3678,7 +3726,7 @@
       <c r="Z9" s="31"/>
       <c r="AA9" s="31"/>
       <c r="AB9" s="31" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="AC9" s="31"/>
       <c r="AD9" s="31"/>
@@ -3726,7 +3774,7 @@
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
       <c r="E10" s="31" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="31"/>
@@ -3751,7 +3799,7 @@
       <c r="Z10" s="31"/>
       <c r="AA10" s="31"/>
       <c r="AB10" s="31" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="AC10" s="31"/>
       <c r="AD10" s="31"/>
@@ -3799,7 +3847,7 @@
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
       <c r="E11" s="31" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="31"/>
@@ -3824,7 +3872,7 @@
       <c r="Z11" s="31"/>
       <c r="AA11" s="31"/>
       <c r="AB11" s="31" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="AC11" s="31"/>
       <c r="AD11" s="31"/>
@@ -3872,7 +3920,7 @@
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
       <c r="E12" s="31" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F12" s="31"/>
       <c r="G12" s="31"/>
@@ -3897,7 +3945,7 @@
       <c r="Z12" s="31"/>
       <c r="AA12" s="31"/>
       <c r="AB12" s="31" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="AC12" s="31"/>
       <c r="AD12" s="31"/>
@@ -3945,7 +3993,7 @@
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
       <c r="E13" s="31" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
@@ -3970,7 +4018,7 @@
       <c r="Z13" s="31"/>
       <c r="AA13" s="31"/>
       <c r="AB13" s="31" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="AC13" s="31"/>
       <c r="AD13" s="31"/>
@@ -4018,7 +4066,7 @@
       <c r="C14" s="26"/>
       <c r="D14" s="26"/>
       <c r="E14" s="31" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="F14" s="31"/>
       <c r="G14" s="31"/>
@@ -4043,7 +4091,7 @@
       <c r="Z14" s="31"/>
       <c r="AA14" s="31"/>
       <c r="AB14" s="31" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="AC14" s="31"/>
       <c r="AD14" s="31"/>
@@ -4328,6 +4376,7 @@
     <mergeCell ref="AB14:BB14"/>
     <mergeCell ref="BC14:BG14"/>
     <mergeCell ref="BH14:BK14"/>
+    <mergeCell ref="BH13:BK13"/>
     <mergeCell ref="BL8:BN8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E9:AA9"/>
@@ -4365,7 +4414,6 @@
     <mergeCell ref="E4:AA4"/>
     <mergeCell ref="AB4:BB4"/>
     <mergeCell ref="BC4:BG4"/>
-    <mergeCell ref="BH13:BK13"/>
     <mergeCell ref="BL13:BN13"/>
     <mergeCell ref="BL10:BN10"/>
     <mergeCell ref="B12:D12"/>
@@ -4530,7 +4578,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="27" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -4603,7 +4651,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -4774,7 +4822,7 @@
       <c r="Z8" s="31"/>
       <c r="AA8" s="31"/>
       <c r="AB8" s="31" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="AC8" s="31"/>
       <c r="AD8" s="31"/>
@@ -4847,7 +4895,7 @@
       <c r="Z9" s="31"/>
       <c r="AA9" s="31"/>
       <c r="AB9" s="31" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="AC9" s="31"/>
       <c r="AD9" s="31"/>
@@ -5455,7 +5503,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="27" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -5528,7 +5576,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -5699,7 +5747,7 @@
       <c r="Z8" s="31"/>
       <c r="AA8" s="31"/>
       <c r="AB8" s="31" t="s">
-        <v>99</v>
+        <v>163</v>
       </c>
       <c r="AC8" s="31"/>
       <c r="AD8" s="31"/>
@@ -5747,7 +5795,7 @@
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
       <c r="E9" s="31" t="s">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
@@ -5772,7 +5820,7 @@
       <c r="Z9" s="31"/>
       <c r="AA9" s="31"/>
       <c r="AB9" s="31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AC9" s="31"/>
       <c r="AD9" s="31"/>
@@ -6302,7 +6350,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="27" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -6375,7 +6423,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -6667,7 +6715,7 @@
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
       <c r="E10" s="31" t="s">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="31"/>
@@ -6692,7 +6740,7 @@
       <c r="Z10" s="31"/>
       <c r="AA10" s="31"/>
       <c r="AB10" s="31" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="AC10" s="31"/>
       <c r="AD10" s="31"/>
@@ -6740,7 +6788,7 @@
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
       <c r="E11" s="31" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="31"/>
@@ -6765,7 +6813,7 @@
       <c r="Z11" s="31"/>
       <c r="AA11" s="31"/>
       <c r="AB11" s="31" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="AC11" s="31"/>
       <c r="AD11" s="31"/>
@@ -6813,7 +6861,7 @@
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
       <c r="E12" s="31" t="s">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="F12" s="31"/>
       <c r="G12" s="31"/>
@@ -6838,7 +6886,7 @@
       <c r="Z12" s="31"/>
       <c r="AA12" s="31"/>
       <c r="AB12" s="31" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="AC12" s="31"/>
       <c r="AD12" s="31"/>
@@ -6886,7 +6934,7 @@
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
       <c r="E13" s="31" t="s">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
@@ -6911,7 +6959,7 @@
       <c r="Z13" s="31"/>
       <c r="AA13" s="31"/>
       <c r="AB13" s="31" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="AC13" s="31"/>
       <c r="AD13" s="31"/>
@@ -6959,7 +7007,7 @@
       <c r="C14" s="26"/>
       <c r="D14" s="26"/>
       <c r="E14" s="31" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="F14" s="31"/>
       <c r="G14" s="31"/>
@@ -6984,7 +7032,7 @@
       <c r="Z14" s="31"/>
       <c r="AA14" s="31"/>
       <c r="AB14" s="31" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="AC14" s="31"/>
       <c r="AD14" s="31"/>
@@ -7247,7 +7295,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="27" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -7320,7 +7368,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -7393,7 +7441,7 @@
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="31" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
@@ -7466,7 +7514,7 @@
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
       <c r="E8" s="31" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
@@ -7491,7 +7539,7 @@
       <c r="Z8" s="31"/>
       <c r="AA8" s="31"/>
       <c r="AB8" s="31" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="AC8" s="31"/>
       <c r="AD8" s="31"/>
@@ -7539,7 +7587,7 @@
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
       <c r="E9" s="31" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
@@ -7564,7 +7612,7 @@
       <c r="Z9" s="31"/>
       <c r="AA9" s="31"/>
       <c r="AB9" s="31" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="AC9" s="31"/>
       <c r="AD9" s="31"/>
@@ -7612,7 +7660,7 @@
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
       <c r="E10" s="31" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="31"/>
@@ -7637,7 +7685,7 @@
       <c r="Z10" s="31"/>
       <c r="AA10" s="31"/>
       <c r="AB10" s="31" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AC10" s="31"/>
       <c r="AD10" s="31"/>
@@ -7685,7 +7733,7 @@
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
       <c r="E11" s="31" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="31"/>
@@ -7710,7 +7758,7 @@
       <c r="Z11" s="31"/>
       <c r="AA11" s="31"/>
       <c r="AB11" s="31" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="AC11" s="31"/>
       <c r="AD11" s="31"/>
@@ -7758,7 +7806,7 @@
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
       <c r="E12" s="31" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F12" s="31"/>
       <c r="G12" s="31"/>
@@ -7783,7 +7831,7 @@
       <c r="Z12" s="31"/>
       <c r="AA12" s="31"/>
       <c r="AB12" s="31" t="s">
-        <v>122</v>
+        <v>173</v>
       </c>
       <c r="AC12" s="31"/>
       <c r="AD12" s="31"/>
@@ -8031,7 +8079,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="27" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -8104,7 +8152,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -8177,7 +8225,7 @@
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="31" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
@@ -8250,7 +8298,7 @@
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
       <c r="E8" s="31" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
@@ -8275,7 +8323,7 @@
       <c r="Z8" s="31"/>
       <c r="AA8" s="31"/>
       <c r="AB8" s="31" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="AC8" s="31"/>
       <c r="AD8" s="31"/>
@@ -8323,7 +8371,7 @@
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
       <c r="E9" s="31" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
@@ -8348,7 +8396,7 @@
       <c r="Z9" s="31"/>
       <c r="AA9" s="31"/>
       <c r="AB9" s="31" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="AC9" s="31"/>
       <c r="AD9" s="31"/>
@@ -8389,14 +8437,14 @@
       <c r="BM9" s="33"/>
       <c r="BN9" s="33"/>
     </row>
-    <row r="10" spans="1:66" ht="144.6" customHeight="1">
+    <row r="10" spans="1:66" ht="181.5" customHeight="1">
       <c r="B10" s="26">
         <v>6</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
       <c r="E10" s="31" t="s">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="31"/>
@@ -8421,7 +8469,7 @@
       <c r="Z10" s="31"/>
       <c r="AA10" s="31"/>
       <c r="AB10" s="31" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="AC10" s="31"/>
       <c r="AD10" s="31"/>
@@ -8469,7 +8517,7 @@
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
       <c r="E11" s="31" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="31"/>
@@ -8494,7 +8542,7 @@
       <c r="Z11" s="31"/>
       <c r="AA11" s="31"/>
       <c r="AB11" s="31" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="AC11" s="31"/>
       <c r="AD11" s="31"/>
@@ -8542,7 +8590,7 @@
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
       <c r="E12" s="31" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F12" s="31"/>
       <c r="G12" s="31"/>
@@ -8567,7 +8615,7 @@
       <c r="Z12" s="31"/>
       <c r="AA12" s="31"/>
       <c r="AB12" s="31" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="AC12" s="31"/>
       <c r="AD12" s="31"/>
@@ -8826,7 +8874,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.390277777777778" right="0.390277777777778" top="0.390277777777778" bottom="0.390277777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="64" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="61" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8967,7 +9015,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="27" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -9040,7 +9088,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="35" t="s">
-        <v>125</v>
+        <v>174</v>
       </c>
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
@@ -9065,7 +9113,7 @@
       <c r="Z6" s="36"/>
       <c r="AA6" s="37"/>
       <c r="AB6" s="31" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="AC6" s="31"/>
       <c r="AD6" s="31"/>
@@ -9113,7 +9161,7 @@
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="31" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
@@ -9138,7 +9186,7 @@
       <c r="Z7" s="31"/>
       <c r="AA7" s="31"/>
       <c r="AB7" s="31" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="AC7" s="31"/>
       <c r="AD7" s="31"/>
@@ -9278,7 +9326,7 @@
       <c r="Z9" s="31"/>
       <c r="AA9" s="31"/>
       <c r="AB9" s="31" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="AC9" s="31"/>
       <c r="AD9" s="31"/>
@@ -9751,7 +9799,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:IW17"/>
+  <dimension ref="A1:IW15"/>
   <sheetFormatPr defaultColWidth="2.7109375" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="4" width="2.7109375" style="8"/>
@@ -9883,7 +9931,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="27" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -9956,7 +10004,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="35" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
@@ -9981,7 +10029,7 @@
       <c r="Z6" s="36"/>
       <c r="AA6" s="37"/>
       <c r="AB6" s="31" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="AC6" s="31"/>
       <c r="AD6" s="31"/>
@@ -10029,7 +10077,7 @@
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="31" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
@@ -10054,7 +10102,7 @@
       <c r="Z7" s="31"/>
       <c r="AA7" s="31"/>
       <c r="AB7" s="31" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="AC7" s="31"/>
       <c r="AD7" s="31"/>
@@ -10095,14 +10143,14 @@
       <c r="BM7" s="33"/>
       <c r="BN7" s="33"/>
     </row>
-    <row r="8" spans="1:66" ht="69.599999999999994" customHeight="1">
+    <row r="8" spans="1:66" ht="87.75" customHeight="1">
       <c r="B8" s="26">
         <v>4</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
       <c r="E8" s="31" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
@@ -10127,7 +10175,7 @@
       <c r="Z8" s="31"/>
       <c r="AA8" s="31"/>
       <c r="AB8" s="31" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="AC8" s="31"/>
       <c r="AD8" s="31"/>
@@ -10168,14 +10216,1035 @@
       <c r="BM8" s="33"/>
       <c r="BN8" s="33"/>
     </row>
-    <row r="9" spans="1:66" ht="85.5" customHeight="1">
+    <row r="9" spans="1:66" ht="103.5" customHeight="1">
+      <c r="B9" s="26">
+        <v>5</v>
+      </c>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+      <c r="Y9" s="36"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="AC9" s="36"/>
+      <c r="AD9" s="36"/>
+      <c r="AE9" s="36"/>
+      <c r="AF9" s="36"/>
+      <c r="AG9" s="36"/>
+      <c r="AH9" s="36"/>
+      <c r="AI9" s="36"/>
+      <c r="AJ9" s="36"/>
+      <c r="AK9" s="36"/>
+      <c r="AL9" s="36"/>
+      <c r="AM9" s="36"/>
+      <c r="AN9" s="36"/>
+      <c r="AO9" s="36"/>
+      <c r="AP9" s="36"/>
+      <c r="AQ9" s="36"/>
+      <c r="AR9" s="36"/>
+      <c r="AS9" s="36"/>
+      <c r="AT9" s="36"/>
+      <c r="AU9" s="36"/>
+      <c r="AV9" s="36"/>
+      <c r="AW9" s="36"/>
+      <c r="AX9" s="36"/>
+      <c r="AY9" s="36"/>
+      <c r="AZ9" s="36"/>
+      <c r="BA9" s="36"/>
+      <c r="BB9" s="37"/>
+      <c r="BC9" s="32"/>
+      <c r="BD9" s="32"/>
+      <c r="BE9" s="32"/>
+      <c r="BF9" s="32"/>
+      <c r="BG9" s="32"/>
+      <c r="BH9" s="33"/>
+      <c r="BI9" s="33"/>
+      <c r="BJ9" s="33"/>
+      <c r="BK9" s="33"/>
+      <c r="BL9" s="33"/>
+      <c r="BM9" s="33"/>
+      <c r="BN9" s="33"/>
+    </row>
+    <row r="10" spans="1:66" ht="92.25" customHeight="1">
+      <c r="B10" s="26">
+        <v>6</v>
+      </c>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="31"/>
+      <c r="AE10" s="31"/>
+      <c r="AF10" s="31"/>
+      <c r="AG10" s="31"/>
+      <c r="AH10" s="31"/>
+      <c r="AI10" s="31"/>
+      <c r="AJ10" s="31"/>
+      <c r="AK10" s="31"/>
+      <c r="AL10" s="31"/>
+      <c r="AM10" s="31"/>
+      <c r="AN10" s="31"/>
+      <c r="AO10" s="31"/>
+      <c r="AP10" s="31"/>
+      <c r="AQ10" s="31"/>
+      <c r="AR10" s="31"/>
+      <c r="AS10" s="31"/>
+      <c r="AT10" s="31"/>
+      <c r="AU10" s="31"/>
+      <c r="AV10" s="31"/>
+      <c r="AW10" s="31"/>
+      <c r="AX10" s="31"/>
+      <c r="AY10" s="31"/>
+      <c r="AZ10" s="31"/>
+      <c r="BA10" s="31"/>
+      <c r="BB10" s="31"/>
+      <c r="BC10" s="41"/>
+      <c r="BD10" s="42"/>
+      <c r="BE10" s="42"/>
+      <c r="BF10" s="42"/>
+      <c r="BG10" s="43"/>
+      <c r="BH10" s="38"/>
+      <c r="BI10" s="39"/>
+      <c r="BJ10" s="39"/>
+      <c r="BK10" s="40"/>
+      <c r="BL10" s="38"/>
+      <c r="BM10" s="39"/>
+      <c r="BN10" s="40"/>
+    </row>
+    <row r="11" spans="1:66" ht="83.25" customHeight="1">
+      <c r="B11" s="26">
+        <v>7</v>
+      </c>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="31"/>
+      <c r="AE11" s="31"/>
+      <c r="AF11" s="31"/>
+      <c r="AG11" s="31"/>
+      <c r="AH11" s="31"/>
+      <c r="AI11" s="31"/>
+      <c r="AJ11" s="31"/>
+      <c r="AK11" s="31"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="31"/>
+      <c r="AN11" s="31"/>
+      <c r="AO11" s="31"/>
+      <c r="AP11" s="31"/>
+      <c r="AQ11" s="31"/>
+      <c r="AR11" s="31"/>
+      <c r="AS11" s="31"/>
+      <c r="AT11" s="31"/>
+      <c r="AU11" s="31"/>
+      <c r="AV11" s="31"/>
+      <c r="AW11" s="31"/>
+      <c r="AX11" s="31"/>
+      <c r="AY11" s="31"/>
+      <c r="AZ11" s="31"/>
+      <c r="BA11" s="31"/>
+      <c r="BB11" s="31"/>
+      <c r="BC11" s="32"/>
+      <c r="BD11" s="32"/>
+      <c r="BE11" s="32"/>
+      <c r="BF11" s="32"/>
+      <c r="BG11" s="32"/>
+      <c r="BH11" s="33"/>
+      <c r="BI11" s="33"/>
+      <c r="BJ11" s="33"/>
+      <c r="BK11" s="33"/>
+      <c r="BL11" s="33"/>
+      <c r="BM11" s="33"/>
+      <c r="BN11" s="33"/>
+    </row>
+    <row r="12" spans="1:66" ht="87" customHeight="1">
+      <c r="B12" s="26">
+        <v>8</v>
+      </c>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="31"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="31"/>
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="31"/>
+      <c r="AH12" s="31"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="31"/>
+      <c r="AK12" s="31"/>
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="31"/>
+      <c r="AN12" s="31"/>
+      <c r="AO12" s="31"/>
+      <c r="AP12" s="31"/>
+      <c r="AQ12" s="31"/>
+      <c r="AR12" s="31"/>
+      <c r="AS12" s="31"/>
+      <c r="AT12" s="31"/>
+      <c r="AU12" s="31"/>
+      <c r="AV12" s="31"/>
+      <c r="AW12" s="31"/>
+      <c r="AX12" s="31"/>
+      <c r="AY12" s="31"/>
+      <c r="AZ12" s="31"/>
+      <c r="BA12" s="31"/>
+      <c r="BB12" s="31"/>
+      <c r="BC12" s="32"/>
+      <c r="BD12" s="32"/>
+      <c r="BE12" s="32"/>
+      <c r="BF12" s="32"/>
+      <c r="BG12" s="32"/>
+      <c r="BH12" s="33"/>
+      <c r="BI12" s="33"/>
+      <c r="BJ12" s="33"/>
+      <c r="BK12" s="33"/>
+      <c r="BL12" s="33"/>
+      <c r="BM12" s="33"/>
+      <c r="BN12" s="33"/>
+    </row>
+    <row r="13" spans="1:66" ht="90.75" customHeight="1">
+      <c r="B13" s="26">
+        <v>9</v>
+      </c>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="31"/>
+      <c r="AB13" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="31"/>
+      <c r="AE13" s="31"/>
+      <c r="AF13" s="31"/>
+      <c r="AG13" s="31"/>
+      <c r="AH13" s="31"/>
+      <c r="AI13" s="31"/>
+      <c r="AJ13" s="31"/>
+      <c r="AK13" s="31"/>
+      <c r="AL13" s="31"/>
+      <c r="AM13" s="31"/>
+      <c r="AN13" s="31"/>
+      <c r="AO13" s="31"/>
+      <c r="AP13" s="31"/>
+      <c r="AQ13" s="31"/>
+      <c r="AR13" s="31"/>
+      <c r="AS13" s="31"/>
+      <c r="AT13" s="31"/>
+      <c r="AU13" s="31"/>
+      <c r="AV13" s="31"/>
+      <c r="AW13" s="31"/>
+      <c r="AX13" s="31"/>
+      <c r="AY13" s="31"/>
+      <c r="AZ13" s="31"/>
+      <c r="BA13" s="31"/>
+      <c r="BB13" s="31"/>
+      <c r="BC13" s="32"/>
+      <c r="BD13" s="32"/>
+      <c r="BE13" s="32"/>
+      <c r="BF13" s="32"/>
+      <c r="BG13" s="32"/>
+      <c r="BH13" s="33"/>
+      <c r="BI13" s="33"/>
+      <c r="BJ13" s="33"/>
+      <c r="BK13" s="33"/>
+      <c r="BL13" s="33"/>
+      <c r="BM13" s="33"/>
+      <c r="BN13" s="33"/>
+    </row>
+    <row r="14" spans="1:66" ht="106.5" customHeight="1">
+      <c r="B14" s="26">
+        <v>10</v>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="31"/>
+      <c r="V14" s="31"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="31"/>
+      <c r="Y14" s="31"/>
+      <c r="Z14" s="31"/>
+      <c r="AA14" s="31"/>
+      <c r="AB14" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC14" s="31"/>
+      <c r="AD14" s="31"/>
+      <c r="AE14" s="31"/>
+      <c r="AF14" s="31"/>
+      <c r="AG14" s="31"/>
+      <c r="AH14" s="31"/>
+      <c r="AI14" s="31"/>
+      <c r="AJ14" s="31"/>
+      <c r="AK14" s="31"/>
+      <c r="AL14" s="31"/>
+      <c r="AM14" s="31"/>
+      <c r="AN14" s="31"/>
+      <c r="AO14" s="31"/>
+      <c r="AP14" s="31"/>
+      <c r="AQ14" s="31"/>
+      <c r="AR14" s="31"/>
+      <c r="AS14" s="31"/>
+      <c r="AT14" s="31"/>
+      <c r="AU14" s="31"/>
+      <c r="AV14" s="31"/>
+      <c r="AW14" s="31"/>
+      <c r="AX14" s="31"/>
+      <c r="AY14" s="31"/>
+      <c r="AZ14" s="31"/>
+      <c r="BA14" s="31"/>
+      <c r="BB14" s="31"/>
+      <c r="BC14" s="32"/>
+      <c r="BD14" s="32"/>
+      <c r="BE14" s="32"/>
+      <c r="BF14" s="32"/>
+      <c r="BG14" s="32"/>
+      <c r="BH14" s="33"/>
+      <c r="BI14" s="33"/>
+      <c r="BJ14" s="33"/>
+      <c r="BK14" s="33"/>
+      <c r="BL14" s="33"/>
+      <c r="BM14" s="33"/>
+      <c r="BN14" s="33"/>
+    </row>
+    <row r="15" spans="1:66" ht="69.599999999999994" customHeight="1">
+      <c r="B15" s="26">
+        <v>11</v>
+      </c>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="31"/>
+      <c r="V15" s="31"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="31"/>
+      <c r="Z15" s="31"/>
+      <c r="AA15" s="31"/>
+      <c r="AB15" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="AC15" s="31"/>
+      <c r="AD15" s="31"/>
+      <c r="AE15" s="31"/>
+      <c r="AF15" s="31"/>
+      <c r="AG15" s="31"/>
+      <c r="AH15" s="31"/>
+      <c r="AI15" s="31"/>
+      <c r="AJ15" s="31"/>
+      <c r="AK15" s="31"/>
+      <c r="AL15" s="31"/>
+      <c r="AM15" s="31"/>
+      <c r="AN15" s="31"/>
+      <c r="AO15" s="31"/>
+      <c r="AP15" s="31"/>
+      <c r="AQ15" s="31"/>
+      <c r="AR15" s="31"/>
+      <c r="AS15" s="31"/>
+      <c r="AT15" s="31"/>
+      <c r="AU15" s="31"/>
+      <c r="AV15" s="31"/>
+      <c r="AW15" s="31"/>
+      <c r="AX15" s="31"/>
+      <c r="AY15" s="31"/>
+      <c r="AZ15" s="31"/>
+      <c r="BA15" s="31"/>
+      <c r="BB15" s="31"/>
+      <c r="BC15" s="32"/>
+      <c r="BD15" s="32"/>
+      <c r="BE15" s="32"/>
+      <c r="BF15" s="32"/>
+      <c r="BG15" s="32"/>
+      <c r="BH15" s="33"/>
+      <c r="BI15" s="33"/>
+      <c r="BJ15" s="33"/>
+      <c r="BK15" s="33"/>
+      <c r="BL15" s="33"/>
+      <c r="BM15" s="33"/>
+      <c r="BN15" s="33"/>
+    </row>
+  </sheetData>
+  <mergeCells count="73">
+    <mergeCell ref="AB11:BB11"/>
+    <mergeCell ref="BC11:BG11"/>
+    <mergeCell ref="BH11:BK11"/>
+    <mergeCell ref="BL11:BN11"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:AA10"/>
+    <mergeCell ref="AB10:BB10"/>
+    <mergeCell ref="BC10:BG10"/>
+    <mergeCell ref="BH10:BK10"/>
+    <mergeCell ref="BL10:BN10"/>
+    <mergeCell ref="BL14:BN14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:AA15"/>
+    <mergeCell ref="AB15:BB15"/>
+    <mergeCell ref="BC15:BG15"/>
+    <mergeCell ref="BH15:BK15"/>
+    <mergeCell ref="BL15:BN15"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:AA14"/>
+    <mergeCell ref="AB14:BB14"/>
+    <mergeCell ref="BC14:BG14"/>
+    <mergeCell ref="BH14:BK14"/>
+    <mergeCell ref="AB9:BB9"/>
+    <mergeCell ref="E9:AA9"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E11:AA11"/>
+    <mergeCell ref="BL12:BN12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:AA13"/>
+    <mergeCell ref="AB13:BB13"/>
+    <mergeCell ref="BC13:BG13"/>
+    <mergeCell ref="BH13:BK13"/>
+    <mergeCell ref="BL13:BN13"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:AA12"/>
+    <mergeCell ref="AB12:BB12"/>
+    <mergeCell ref="BC12:BG12"/>
+    <mergeCell ref="BH12:BK12"/>
+    <mergeCell ref="BL8:BN8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="BC9:BG9"/>
+    <mergeCell ref="BH9:BK9"/>
+    <mergeCell ref="BL9:BN9"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:AA8"/>
+    <mergeCell ref="AB8:BB8"/>
+    <mergeCell ref="BC8:BG8"/>
+    <mergeCell ref="BH8:BK8"/>
+    <mergeCell ref="BL6:BN6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:AA7"/>
+    <mergeCell ref="AB7:BB7"/>
+    <mergeCell ref="BC7:BG7"/>
+    <mergeCell ref="BH7:BK7"/>
+    <mergeCell ref="BL7:BN7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:AA6"/>
+    <mergeCell ref="AB6:BB6"/>
+    <mergeCell ref="BC6:BG6"/>
+    <mergeCell ref="BH6:BK6"/>
+    <mergeCell ref="BH4:BK4"/>
+    <mergeCell ref="BL4:BN4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:AA5"/>
+    <mergeCell ref="AB5:BB5"/>
+    <mergeCell ref="BC5:BG5"/>
+    <mergeCell ref="BH5:BK5"/>
+    <mergeCell ref="BL5:BN5"/>
+    <mergeCell ref="F2:AA2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:AA4"/>
+    <mergeCell ref="AB4:BB4"/>
+    <mergeCell ref="BC4:BG4"/>
+  </mergeCells>
+  <phoneticPr fontId="20"/>
+  <dataValidations count="1">
+    <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" sqref="BL5:BN15" xr:uid="{00000000-0002-0000-1100-000000000000}">
+      <formula1>"OK,NG"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.390277777777778" right="0.390277777777778" top="0.390277777777778" bottom="0.390277777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="19" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:IW14"/>
+  <sheetFormatPr defaultColWidth="2.7109375" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="4" width="2.7109375" style="8"/>
+    <col min="5" max="9" width="2.7109375" style="9"/>
+    <col min="10" max="257" width="2.7109375" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:66" ht="16.149999999999999" customHeight="1">
+      <c r="A1" s="11"/>
+    </row>
+    <row r="2" spans="1:66" s="12" customFormat="1" ht="15" customHeight="1">
+      <c r="B2" s="20" t="str">
+        <f t="array" aca="1" ref="B2" ca="1">RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1)))</f>
+        <v>ケース17</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="30" t="str">
+        <f>ケース一覧!L21</f>
+        <v>受講生 初回ログイン 正常系</v>
+      </c>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+    </row>
+    <row r="3" spans="1:66" ht="16.899999999999999" customHeight="1"/>
+    <row r="4" spans="1:66" ht="39" customHeight="1">
+      <c r="B4" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="V4" s="25"/>
+      <c r="W4" s="25"/>
+      <c r="X4" s="25"/>
+      <c r="Y4" s="25"/>
+      <c r="Z4" s="25"/>
+      <c r="AA4" s="25"/>
+      <c r="AB4" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC4" s="25"/>
+      <c r="AD4" s="25"/>
+      <c r="AE4" s="25"/>
+      <c r="AF4" s="25"/>
+      <c r="AG4" s="25"/>
+      <c r="AH4" s="25"/>
+      <c r="AI4" s="25"/>
+      <c r="AJ4" s="25"/>
+      <c r="AK4" s="25"/>
+      <c r="AL4" s="25"/>
+      <c r="AM4" s="25"/>
+      <c r="AN4" s="25"/>
+      <c r="AO4" s="25"/>
+      <c r="AP4" s="25"/>
+      <c r="AQ4" s="25"/>
+      <c r="AR4" s="25"/>
+      <c r="AS4" s="25"/>
+      <c r="AT4" s="25"/>
+      <c r="AU4" s="25"/>
+      <c r="AV4" s="25"/>
+      <c r="AW4" s="25"/>
+      <c r="AX4" s="25"/>
+      <c r="AY4" s="25"/>
+      <c r="AZ4" s="25"/>
+      <c r="BA4" s="25"/>
+      <c r="BB4" s="25"/>
+      <c r="BC4" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="BD4" s="25"/>
+      <c r="BE4" s="25"/>
+      <c r="BF4" s="25"/>
+      <c r="BG4" s="25"/>
+      <c r="BH4" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="BI4" s="25"/>
+      <c r="BJ4" s="25"/>
+      <c r="BK4" s="25"/>
+      <c r="BL4" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="BM4" s="25"/>
+      <c r="BN4" s="25"/>
+    </row>
+    <row r="5" spans="1:66" ht="115.9" customHeight="1">
+      <c r="B5" s="26">
+        <v>1</v>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="31"/>
+      <c r="AE5" s="31"/>
+      <c r="AF5" s="31"/>
+      <c r="AG5" s="31"/>
+      <c r="AH5" s="31"/>
+      <c r="AI5" s="31"/>
+      <c r="AJ5" s="31"/>
+      <c r="AK5" s="31"/>
+      <c r="AL5" s="31"/>
+      <c r="AM5" s="31"/>
+      <c r="AN5" s="31"/>
+      <c r="AO5" s="31"/>
+      <c r="AP5" s="31"/>
+      <c r="AQ5" s="31"/>
+      <c r="AR5" s="31"/>
+      <c r="AS5" s="31"/>
+      <c r="AT5" s="31"/>
+      <c r="AU5" s="31"/>
+      <c r="AV5" s="31"/>
+      <c r="AW5" s="31"/>
+      <c r="AX5" s="31"/>
+      <c r="AY5" s="31"/>
+      <c r="AZ5" s="31"/>
+      <c r="BA5" s="31"/>
+      <c r="BB5" s="31"/>
+      <c r="BC5" s="32"/>
+      <c r="BD5" s="32"/>
+      <c r="BE5" s="32"/>
+      <c r="BF5" s="32"/>
+      <c r="BG5" s="32"/>
+      <c r="BH5" s="33"/>
+      <c r="BI5" s="33"/>
+      <c r="BJ5" s="33"/>
+      <c r="BK5" s="33"/>
+      <c r="BL5" s="33"/>
+      <c r="BM5" s="33"/>
+      <c r="BN5" s="33"/>
+    </row>
+    <row r="6" spans="1:66" ht="84.95" customHeight="1">
+      <c r="B6" s="26">
+        <v>2</v>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="36"/>
+      <c r="Z6" s="36"/>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="31"/>
+      <c r="AE6" s="31"/>
+      <c r="AF6" s="31"/>
+      <c r="AG6" s="31"/>
+      <c r="AH6" s="31"/>
+      <c r="AI6" s="31"/>
+      <c r="AJ6" s="31"/>
+      <c r="AK6" s="31"/>
+      <c r="AL6" s="31"/>
+      <c r="AM6" s="31"/>
+      <c r="AN6" s="31"/>
+      <c r="AO6" s="31"/>
+      <c r="AP6" s="31"/>
+      <c r="AQ6" s="31"/>
+      <c r="AR6" s="31"/>
+      <c r="AS6" s="31"/>
+      <c r="AT6" s="31"/>
+      <c r="AU6" s="31"/>
+      <c r="AV6" s="31"/>
+      <c r="AW6" s="31"/>
+      <c r="AX6" s="31"/>
+      <c r="AY6" s="31"/>
+      <c r="AZ6" s="31"/>
+      <c r="BA6" s="31"/>
+      <c r="BB6" s="31"/>
+      <c r="BC6" s="32"/>
+      <c r="BD6" s="32"/>
+      <c r="BE6" s="32"/>
+      <c r="BF6" s="32"/>
+      <c r="BG6" s="32"/>
+      <c r="BH6" s="33"/>
+      <c r="BI6" s="33"/>
+      <c r="BJ6" s="33"/>
+      <c r="BK6" s="33"/>
+      <c r="BL6" s="33"/>
+      <c r="BM6" s="33"/>
+      <c r="BN6" s="33"/>
+    </row>
+    <row r="7" spans="1:66" ht="84.95" customHeight="1">
+      <c r="B7" s="26">
+        <v>3</v>
+      </c>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="31"/>
+      <c r="AB7" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC7" s="31"/>
+      <c r="AD7" s="31"/>
+      <c r="AE7" s="31"/>
+      <c r="AF7" s="31"/>
+      <c r="AG7" s="31"/>
+      <c r="AH7" s="31"/>
+      <c r="AI7" s="31"/>
+      <c r="AJ7" s="31"/>
+      <c r="AK7" s="31"/>
+      <c r="AL7" s="31"/>
+      <c r="AM7" s="31"/>
+      <c r="AN7" s="31"/>
+      <c r="AO7" s="31"/>
+      <c r="AP7" s="31"/>
+      <c r="AQ7" s="31"/>
+      <c r="AR7" s="31"/>
+      <c r="AS7" s="31"/>
+      <c r="AT7" s="31"/>
+      <c r="AU7" s="31"/>
+      <c r="AV7" s="31"/>
+      <c r="AW7" s="31"/>
+      <c r="AX7" s="31"/>
+      <c r="AY7" s="31"/>
+      <c r="AZ7" s="31"/>
+      <c r="BA7" s="31"/>
+      <c r="BB7" s="31"/>
+      <c r="BC7" s="32"/>
+      <c r="BD7" s="32"/>
+      <c r="BE7" s="32"/>
+      <c r="BF7" s="32"/>
+      <c r="BG7" s="32"/>
+      <c r="BH7" s="33"/>
+      <c r="BI7" s="33"/>
+      <c r="BJ7" s="33"/>
+      <c r="BK7" s="33"/>
+      <c r="BL7" s="33"/>
+      <c r="BM7" s="33"/>
+      <c r="BN7" s="33"/>
+    </row>
+    <row r="8" spans="1:66" ht="84.95" customHeight="1">
+      <c r="B8" s="26">
+        <v>4</v>
+      </c>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="31"/>
+      <c r="AF8" s="31"/>
+      <c r="AG8" s="31"/>
+      <c r="AH8" s="31"/>
+      <c r="AI8" s="31"/>
+      <c r="AJ8" s="31"/>
+      <c r="AK8" s="31"/>
+      <c r="AL8" s="31"/>
+      <c r="AM8" s="31"/>
+      <c r="AN8" s="31"/>
+      <c r="AO8" s="31"/>
+      <c r="AP8" s="31"/>
+      <c r="AQ8" s="31"/>
+      <c r="AR8" s="31"/>
+      <c r="AS8" s="31"/>
+      <c r="AT8" s="31"/>
+      <c r="AU8" s="31"/>
+      <c r="AV8" s="31"/>
+      <c r="AW8" s="31"/>
+      <c r="AX8" s="31"/>
+      <c r="AY8" s="31"/>
+      <c r="AZ8" s="31"/>
+      <c r="BA8" s="31"/>
+      <c r="BB8" s="31"/>
+      <c r="BC8" s="32"/>
+      <c r="BD8" s="32"/>
+      <c r="BE8" s="32"/>
+      <c r="BF8" s="32"/>
+      <c r="BG8" s="32"/>
+      <c r="BH8" s="33"/>
+      <c r="BI8" s="33"/>
+      <c r="BJ8" s="33"/>
+      <c r="BK8" s="33"/>
+      <c r="BL8" s="33"/>
+      <c r="BM8" s="33"/>
+      <c r="BN8" s="33"/>
+    </row>
+    <row r="9" spans="1:66" ht="84.95" customHeight="1">
       <c r="B9" s="26">
         <v>5</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
       <c r="E9" s="31" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
@@ -10200,7 +11269,7 @@
       <c r="Z9" s="31"/>
       <c r="AA9" s="31"/>
       <c r="AB9" s="31" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="AC9" s="31"/>
       <c r="AD9" s="31"/>
@@ -10241,14 +11310,14 @@
       <c r="BM9" s="33"/>
       <c r="BN9" s="33"/>
     </row>
-    <row r="10" spans="1:66" ht="72.400000000000006" customHeight="1">
+    <row r="10" spans="1:66" ht="45.95" customHeight="1">
       <c r="B10" s="26">
         <v>6</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
       <c r="E10" s="31" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="31"/>
@@ -10273,7 +11342,7 @@
       <c r="Z10" s="31"/>
       <c r="AA10" s="31"/>
       <c r="AB10" s="31" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="AC10" s="31"/>
       <c r="AD10" s="31"/>
@@ -10314,14 +11383,14 @@
       <c r="BM10" s="33"/>
       <c r="BN10" s="33"/>
     </row>
-    <row r="11" spans="1:66" ht="90.75" customHeight="1">
+    <row r="11" spans="1:66" ht="76.900000000000006" customHeight="1">
       <c r="B11" s="26">
         <v>7</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
       <c r="E11" s="31" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="31"/>
@@ -10346,1186 +11415,7 @@
       <c r="Z11" s="31"/>
       <c r="AA11" s="31"/>
       <c r="AB11" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="AC11" s="31"/>
-      <c r="AD11" s="31"/>
-      <c r="AE11" s="31"/>
-      <c r="AF11" s="31"/>
-      <c r="AG11" s="31"/>
-      <c r="AH11" s="31"/>
-      <c r="AI11" s="31"/>
-      <c r="AJ11" s="31"/>
-      <c r="AK11" s="31"/>
-      <c r="AL11" s="31"/>
-      <c r="AM11" s="31"/>
-      <c r="AN11" s="31"/>
-      <c r="AO11" s="31"/>
-      <c r="AP11" s="31"/>
-      <c r="AQ11" s="31"/>
-      <c r="AR11" s="31"/>
-      <c r="AS11" s="31"/>
-      <c r="AT11" s="31"/>
-      <c r="AU11" s="31"/>
-      <c r="AV11" s="31"/>
-      <c r="AW11" s="31"/>
-      <c r="AX11" s="31"/>
-      <c r="AY11" s="31"/>
-      <c r="AZ11" s="31"/>
-      <c r="BA11" s="31"/>
-      <c r="BB11" s="31"/>
-      <c r="BC11" s="32"/>
-      <c r="BD11" s="32"/>
-      <c r="BE11" s="32"/>
-      <c r="BF11" s="32"/>
-      <c r="BG11" s="32"/>
-      <c r="BH11" s="33"/>
-      <c r="BI11" s="33"/>
-      <c r="BJ11" s="33"/>
-      <c r="BK11" s="33"/>
-      <c r="BL11" s="33"/>
-      <c r="BM11" s="33"/>
-      <c r="BN11" s="33"/>
-    </row>
-    <row r="12" spans="1:66" ht="69.599999999999994" customHeight="1">
-      <c r="B12" s="26">
-        <v>8</v>
-      </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="31"/>
-      <c r="T12" s="31"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="31"/>
-      <c r="W12" s="31"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="31"/>
-      <c r="Z12" s="31"/>
-      <c r="AA12" s="31"/>
-      <c r="AB12" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="AC12" s="31"/>
-      <c r="AD12" s="31"/>
-      <c r="AE12" s="31"/>
-      <c r="AF12" s="31"/>
-      <c r="AG12" s="31"/>
-      <c r="AH12" s="31"/>
-      <c r="AI12" s="31"/>
-      <c r="AJ12" s="31"/>
-      <c r="AK12" s="31"/>
-      <c r="AL12" s="31"/>
-      <c r="AM12" s="31"/>
-      <c r="AN12" s="31"/>
-      <c r="AO12" s="31"/>
-      <c r="AP12" s="31"/>
-      <c r="AQ12" s="31"/>
-      <c r="AR12" s="31"/>
-      <c r="AS12" s="31"/>
-      <c r="AT12" s="31"/>
-      <c r="AU12" s="31"/>
-      <c r="AV12" s="31"/>
-      <c r="AW12" s="31"/>
-      <c r="AX12" s="31"/>
-      <c r="AY12" s="31"/>
-      <c r="AZ12" s="31"/>
-      <c r="BA12" s="31"/>
-      <c r="BB12" s="31"/>
-      <c r="BC12" s="32"/>
-      <c r="BD12" s="32"/>
-      <c r="BE12" s="32"/>
-      <c r="BF12" s="32"/>
-      <c r="BG12" s="32"/>
-      <c r="BH12" s="33"/>
-      <c r="BI12" s="33"/>
-      <c r="BJ12" s="33"/>
-      <c r="BK12" s="33"/>
-      <c r="BL12" s="33"/>
-      <c r="BM12" s="33"/>
-      <c r="BN12" s="33"/>
-    </row>
-    <row r="13" spans="1:66" ht="69.599999999999994" customHeight="1">
-      <c r="B13" s="26">
-        <v>9</v>
-      </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="31"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="31"/>
-      <c r="AA13" s="31"/>
-      <c r="AB13" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="AC13" s="31"/>
-      <c r="AD13" s="31"/>
-      <c r="AE13" s="31"/>
-      <c r="AF13" s="31"/>
-      <c r="AG13" s="31"/>
-      <c r="AH13" s="31"/>
-      <c r="AI13" s="31"/>
-      <c r="AJ13" s="31"/>
-      <c r="AK13" s="31"/>
-      <c r="AL13" s="31"/>
-      <c r="AM13" s="31"/>
-      <c r="AN13" s="31"/>
-      <c r="AO13" s="31"/>
-      <c r="AP13" s="31"/>
-      <c r="AQ13" s="31"/>
-      <c r="AR13" s="31"/>
-      <c r="AS13" s="31"/>
-      <c r="AT13" s="31"/>
-      <c r="AU13" s="31"/>
-      <c r="AV13" s="31"/>
-      <c r="AW13" s="31"/>
-      <c r="AX13" s="31"/>
-      <c r="AY13" s="31"/>
-      <c r="AZ13" s="31"/>
-      <c r="BA13" s="31"/>
-      <c r="BB13" s="31"/>
-      <c r="BC13" s="32"/>
-      <c r="BD13" s="32"/>
-      <c r="BE13" s="32"/>
-      <c r="BF13" s="32"/>
-      <c r="BG13" s="32"/>
-      <c r="BH13" s="33"/>
-      <c r="BI13" s="33"/>
-      <c r="BJ13" s="33"/>
-      <c r="BK13" s="33"/>
-      <c r="BL13" s="33"/>
-      <c r="BM13" s="33"/>
-      <c r="BN13" s="33"/>
-    </row>
-    <row r="14" spans="1:66" ht="69.599999999999994" customHeight="1">
-      <c r="B14" s="26">
-        <v>10</v>
-      </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="31"/>
-      <c r="T14" s="31"/>
-      <c r="U14" s="31"/>
-      <c r="V14" s="31"/>
-      <c r="W14" s="31"/>
-      <c r="X14" s="31"/>
-      <c r="Y14" s="31"/>
-      <c r="Z14" s="31"/>
-      <c r="AA14" s="31"/>
-      <c r="AB14" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="AC14" s="31"/>
-      <c r="AD14" s="31"/>
-      <c r="AE14" s="31"/>
-      <c r="AF14" s="31"/>
-      <c r="AG14" s="31"/>
-      <c r="AH14" s="31"/>
-      <c r="AI14" s="31"/>
-      <c r="AJ14" s="31"/>
-      <c r="AK14" s="31"/>
-      <c r="AL14" s="31"/>
-      <c r="AM14" s="31"/>
-      <c r="AN14" s="31"/>
-      <c r="AO14" s="31"/>
-      <c r="AP14" s="31"/>
-      <c r="AQ14" s="31"/>
-      <c r="AR14" s="31"/>
-      <c r="AS14" s="31"/>
-      <c r="AT14" s="31"/>
-      <c r="AU14" s="31"/>
-      <c r="AV14" s="31"/>
-      <c r="AW14" s="31"/>
-      <c r="AX14" s="31"/>
-      <c r="AY14" s="31"/>
-      <c r="AZ14" s="31"/>
-      <c r="BA14" s="31"/>
-      <c r="BB14" s="31"/>
-      <c r="BC14" s="32"/>
-      <c r="BD14" s="32"/>
-      <c r="BE14" s="32"/>
-      <c r="BF14" s="32"/>
-      <c r="BG14" s="32"/>
-      <c r="BH14" s="33"/>
-      <c r="BI14" s="33"/>
-      <c r="BJ14" s="33"/>
-      <c r="BK14" s="33"/>
-      <c r="BL14" s="33"/>
-      <c r="BM14" s="33"/>
-      <c r="BN14" s="33"/>
-    </row>
-    <row r="15" spans="1:66" ht="69.599999999999994" customHeight="1">
-      <c r="B15" s="26">
-        <v>11</v>
-      </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
-      <c r="T15" s="31"/>
-      <c r="U15" s="31"/>
-      <c r="V15" s="31"/>
-      <c r="W15" s="31"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="31"/>
-      <c r="Z15" s="31"/>
-      <c r="AA15" s="31"/>
-      <c r="AB15" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="AC15" s="31"/>
-      <c r="AD15" s="31"/>
-      <c r="AE15" s="31"/>
-      <c r="AF15" s="31"/>
-      <c r="AG15" s="31"/>
-      <c r="AH15" s="31"/>
-      <c r="AI15" s="31"/>
-      <c r="AJ15" s="31"/>
-      <c r="AK15" s="31"/>
-      <c r="AL15" s="31"/>
-      <c r="AM15" s="31"/>
-      <c r="AN15" s="31"/>
-      <c r="AO15" s="31"/>
-      <c r="AP15" s="31"/>
-      <c r="AQ15" s="31"/>
-      <c r="AR15" s="31"/>
-      <c r="AS15" s="31"/>
-      <c r="AT15" s="31"/>
-      <c r="AU15" s="31"/>
-      <c r="AV15" s="31"/>
-      <c r="AW15" s="31"/>
-      <c r="AX15" s="31"/>
-      <c r="AY15" s="31"/>
-      <c r="AZ15" s="31"/>
-      <c r="BA15" s="31"/>
-      <c r="BB15" s="31"/>
-      <c r="BC15" s="32"/>
-      <c r="BD15" s="32"/>
-      <c r="BE15" s="32"/>
-      <c r="BF15" s="32"/>
-      <c r="BG15" s="32"/>
-      <c r="BH15" s="33"/>
-      <c r="BI15" s="33"/>
-      <c r="BJ15" s="33"/>
-      <c r="BK15" s="33"/>
-      <c r="BL15" s="33"/>
-      <c r="BM15" s="33"/>
-      <c r="BN15" s="33"/>
-    </row>
-    <row r="16" spans="1:66" ht="69.599999999999994" customHeight="1">
-      <c r="B16" s="26">
-        <v>12</v>
-      </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="31"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="31"/>
-      <c r="V16" s="31"/>
-      <c r="W16" s="31"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="31"/>
-      <c r="AA16" s="31"/>
-      <c r="AB16" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="AC16" s="31"/>
-      <c r="AD16" s="31"/>
-      <c r="AE16" s="31"/>
-      <c r="AF16" s="31"/>
-      <c r="AG16" s="31"/>
-      <c r="AH16" s="31"/>
-      <c r="AI16" s="31"/>
-      <c r="AJ16" s="31"/>
-      <c r="AK16" s="31"/>
-      <c r="AL16" s="31"/>
-      <c r="AM16" s="31"/>
-      <c r="AN16" s="31"/>
-      <c r="AO16" s="31"/>
-      <c r="AP16" s="31"/>
-      <c r="AQ16" s="31"/>
-      <c r="AR16" s="31"/>
-      <c r="AS16" s="31"/>
-      <c r="AT16" s="31"/>
-      <c r="AU16" s="31"/>
-      <c r="AV16" s="31"/>
-      <c r="AW16" s="31"/>
-      <c r="AX16" s="31"/>
-      <c r="AY16" s="31"/>
-      <c r="AZ16" s="31"/>
-      <c r="BA16" s="31"/>
-      <c r="BB16" s="31"/>
-      <c r="BC16" s="32"/>
-      <c r="BD16" s="32"/>
-      <c r="BE16" s="32"/>
-      <c r="BF16" s="32"/>
-      <c r="BG16" s="32"/>
-      <c r="BH16" s="33"/>
-      <c r="BI16" s="33"/>
-      <c r="BJ16" s="33"/>
-      <c r="BK16" s="33"/>
-      <c r="BL16" s="33"/>
-      <c r="BM16" s="33"/>
-      <c r="BN16" s="33"/>
-    </row>
-    <row r="17" spans="2:66" ht="112.5" customHeight="1">
-      <c r="B17" s="26">
-        <v>13</v>
-      </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
-      <c r="AA17" s="31"/>
-      <c r="AB17" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="AC17" s="31"/>
-      <c r="AD17" s="31"/>
-      <c r="AE17" s="31"/>
-      <c r="AF17" s="31"/>
-      <c r="AG17" s="31"/>
-      <c r="AH17" s="31"/>
-      <c r="AI17" s="31"/>
-      <c r="AJ17" s="31"/>
-      <c r="AK17" s="31"/>
-      <c r="AL17" s="31"/>
-      <c r="AM17" s="31"/>
-      <c r="AN17" s="31"/>
-      <c r="AO17" s="31"/>
-      <c r="AP17" s="31"/>
-      <c r="AQ17" s="31"/>
-      <c r="AR17" s="31"/>
-      <c r="AS17" s="31"/>
-      <c r="AT17" s="31"/>
-      <c r="AU17" s="31"/>
-      <c r="AV17" s="31"/>
-      <c r="AW17" s="31"/>
-      <c r="AX17" s="31"/>
-      <c r="AY17" s="31"/>
-      <c r="AZ17" s="31"/>
-      <c r="BA17" s="31"/>
-      <c r="BB17" s="31"/>
-      <c r="BC17" s="32"/>
-      <c r="BD17" s="32"/>
-      <c r="BE17" s="32"/>
-      <c r="BF17" s="32"/>
-      <c r="BG17" s="32"/>
-      <c r="BH17" s="33"/>
-      <c r="BI17" s="33"/>
-      <c r="BJ17" s="33"/>
-      <c r="BK17" s="33"/>
-      <c r="BL17" s="33"/>
-      <c r="BM17" s="33"/>
-      <c r="BN17" s="33"/>
-    </row>
-  </sheetData>
-  <mergeCells count="85">
-    <mergeCell ref="BL16:BN16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:AA17"/>
-    <mergeCell ref="AB17:BB17"/>
-    <mergeCell ref="BC17:BG17"/>
-    <mergeCell ref="BH17:BK17"/>
-    <mergeCell ref="BL17:BN17"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:AA16"/>
-    <mergeCell ref="AB16:BB16"/>
-    <mergeCell ref="BC16:BG16"/>
-    <mergeCell ref="BH16:BK16"/>
-    <mergeCell ref="BL14:BN14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:AA15"/>
-    <mergeCell ref="AB15:BB15"/>
-    <mergeCell ref="BC15:BG15"/>
-    <mergeCell ref="BH15:BK15"/>
-    <mergeCell ref="BL15:BN15"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:AA14"/>
-    <mergeCell ref="AB14:BB14"/>
-    <mergeCell ref="BC14:BG14"/>
-    <mergeCell ref="BH14:BK14"/>
-    <mergeCell ref="BL12:BN12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:AA13"/>
-    <mergeCell ref="AB13:BB13"/>
-    <mergeCell ref="BC13:BG13"/>
-    <mergeCell ref="BH13:BK13"/>
-    <mergeCell ref="BL13:BN13"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:AA12"/>
-    <mergeCell ref="AB12:BB12"/>
-    <mergeCell ref="BC12:BG12"/>
-    <mergeCell ref="BH12:BK12"/>
-    <mergeCell ref="BL10:BN10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E11:AA11"/>
-    <mergeCell ref="AB11:BB11"/>
-    <mergeCell ref="BC11:BG11"/>
-    <mergeCell ref="BH11:BK11"/>
-    <mergeCell ref="BL11:BN11"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:AA10"/>
-    <mergeCell ref="AB10:BB10"/>
-    <mergeCell ref="BC10:BG10"/>
-    <mergeCell ref="BH10:BK10"/>
-    <mergeCell ref="BL8:BN8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:AA9"/>
-    <mergeCell ref="AB9:BB9"/>
-    <mergeCell ref="BC9:BG9"/>
-    <mergeCell ref="BH9:BK9"/>
-    <mergeCell ref="BL9:BN9"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:AA8"/>
-    <mergeCell ref="AB8:BB8"/>
-    <mergeCell ref="BC8:BG8"/>
-    <mergeCell ref="BH8:BK8"/>
-    <mergeCell ref="BL6:BN6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:AA7"/>
-    <mergeCell ref="AB7:BB7"/>
-    <mergeCell ref="BC7:BG7"/>
-    <mergeCell ref="BH7:BK7"/>
-    <mergeCell ref="BL7:BN7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:AA6"/>
-    <mergeCell ref="AB6:BB6"/>
-    <mergeCell ref="BC6:BG6"/>
-    <mergeCell ref="BH6:BK6"/>
-    <mergeCell ref="BH4:BK4"/>
-    <mergeCell ref="BL4:BN4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:AA5"/>
-    <mergeCell ref="AB5:BB5"/>
-    <mergeCell ref="BC5:BG5"/>
-    <mergeCell ref="BH5:BK5"/>
-    <mergeCell ref="BL5:BN5"/>
-    <mergeCell ref="F2:AA2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:AA4"/>
-    <mergeCell ref="AB4:BB4"/>
-    <mergeCell ref="BC4:BG4"/>
-  </mergeCells>
-  <phoneticPr fontId="20"/>
-  <dataValidations count="1">
-    <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" sqref="BL5:BN17" xr:uid="{00000000-0002-0000-1100-000000000000}">
-      <formula1>"OK,NG"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.390277777777778" right="0.390277777777778" top="0.390277777777778" bottom="0.390277777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="48" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:IW14"/>
-  <sheetFormatPr defaultColWidth="2.7109375" defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="4" width="2.7109375" style="8"/>
-    <col min="5" max="9" width="2.7109375" style="9"/>
-    <col min="10" max="257" width="2.7109375" style="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:66" ht="16.149999999999999" customHeight="1">
-      <c r="A1" s="11"/>
-    </row>
-    <row r="2" spans="1:66" s="12" customFormat="1" ht="15" customHeight="1">
-      <c r="B2" s="20" t="str">
-        <f t="array" aca="1" ref="B2" ca="1">RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1)))</f>
-        <v>ケース17</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="30" t="str">
-        <f>ケース一覧!L21</f>
-        <v>受講生 初回ログイン 正常系</v>
-      </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-    </row>
-    <row r="3" spans="1:66" ht="16.899999999999999" customHeight="1"/>
-    <row r="4" spans="1:66" ht="39" customHeight="1">
-      <c r="B4" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="V4" s="25"/>
-      <c r="W4" s="25"/>
-      <c r="X4" s="25"/>
-      <c r="Y4" s="25"/>
-      <c r="Z4" s="25"/>
-      <c r="AA4" s="25"/>
-      <c r="AB4" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC4" s="25"/>
-      <c r="AD4" s="25"/>
-      <c r="AE4" s="25"/>
-      <c r="AF4" s="25"/>
-      <c r="AG4" s="25"/>
-      <c r="AH4" s="25"/>
-      <c r="AI4" s="25"/>
-      <c r="AJ4" s="25"/>
-      <c r="AK4" s="25"/>
-      <c r="AL4" s="25"/>
-      <c r="AM4" s="25"/>
-      <c r="AN4" s="25"/>
-      <c r="AO4" s="25"/>
-      <c r="AP4" s="25"/>
-      <c r="AQ4" s="25"/>
-      <c r="AR4" s="25"/>
-      <c r="AS4" s="25"/>
-      <c r="AT4" s="25"/>
-      <c r="AU4" s="25"/>
-      <c r="AV4" s="25"/>
-      <c r="AW4" s="25"/>
-      <c r="AX4" s="25"/>
-      <c r="AY4" s="25"/>
-      <c r="AZ4" s="25"/>
-      <c r="BA4" s="25"/>
-      <c r="BB4" s="25"/>
-      <c r="BC4" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="BD4" s="25"/>
-      <c r="BE4" s="25"/>
-      <c r="BF4" s="25"/>
-      <c r="BG4" s="25"/>
-      <c r="BH4" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="BI4" s="25"/>
-      <c r="BJ4" s="25"/>
-      <c r="BK4" s="25"/>
-      <c r="BL4" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="BM4" s="25"/>
-      <c r="BN4" s="25"/>
-    </row>
-    <row r="5" spans="1:66" ht="115.9" customHeight="1">
-      <c r="B5" s="26">
-        <v>1</v>
-      </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-      <c r="W5" s="27"/>
-      <c r="X5" s="27"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="27"/>
-      <c r="AB5" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC5" s="31"/>
-      <c r="AD5" s="31"/>
-      <c r="AE5" s="31"/>
-      <c r="AF5" s="31"/>
-      <c r="AG5" s="31"/>
-      <c r="AH5" s="31"/>
-      <c r="AI5" s="31"/>
-      <c r="AJ5" s="31"/>
-      <c r="AK5" s="31"/>
-      <c r="AL5" s="31"/>
-      <c r="AM5" s="31"/>
-      <c r="AN5" s="31"/>
-      <c r="AO5" s="31"/>
-      <c r="AP5" s="31"/>
-      <c r="AQ5" s="31"/>
-      <c r="AR5" s="31"/>
-      <c r="AS5" s="31"/>
-      <c r="AT5" s="31"/>
-      <c r="AU5" s="31"/>
-      <c r="AV5" s="31"/>
-      <c r="AW5" s="31"/>
-      <c r="AX5" s="31"/>
-      <c r="AY5" s="31"/>
-      <c r="AZ5" s="31"/>
-      <c r="BA5" s="31"/>
-      <c r="BB5" s="31"/>
-      <c r="BC5" s="32"/>
-      <c r="BD5" s="32"/>
-      <c r="BE5" s="32"/>
-      <c r="BF5" s="32"/>
-      <c r="BG5" s="32"/>
-      <c r="BH5" s="33"/>
-      <c r="BI5" s="33"/>
-      <c r="BJ5" s="33"/>
-      <c r="BK5" s="33"/>
-      <c r="BL5" s="33"/>
-      <c r="BM5" s="33"/>
-      <c r="BN5" s="33"/>
-    </row>
-    <row r="6" spans="1:66" ht="84.95" customHeight="1">
-      <c r="B6" s="26">
-        <v>2</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="37"/>
-      <c r="AB6" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="AC6" s="31"/>
-      <c r="AD6" s="31"/>
-      <c r="AE6" s="31"/>
-      <c r="AF6" s="31"/>
-      <c r="AG6" s="31"/>
-      <c r="AH6" s="31"/>
-      <c r="AI6" s="31"/>
-      <c r="AJ6" s="31"/>
-      <c r="AK6" s="31"/>
-      <c r="AL6" s="31"/>
-      <c r="AM6" s="31"/>
-      <c r="AN6" s="31"/>
-      <c r="AO6" s="31"/>
-      <c r="AP6" s="31"/>
-      <c r="AQ6" s="31"/>
-      <c r="AR6" s="31"/>
-      <c r="AS6" s="31"/>
-      <c r="AT6" s="31"/>
-      <c r="AU6" s="31"/>
-      <c r="AV6" s="31"/>
-      <c r="AW6" s="31"/>
-      <c r="AX6" s="31"/>
-      <c r="AY6" s="31"/>
-      <c r="AZ6" s="31"/>
-      <c r="BA6" s="31"/>
-      <c r="BB6" s="31"/>
-      <c r="BC6" s="32"/>
-      <c r="BD6" s="32"/>
-      <c r="BE6" s="32"/>
-      <c r="BF6" s="32"/>
-      <c r="BG6" s="32"/>
-      <c r="BH6" s="33"/>
-      <c r="BI6" s="33"/>
-      <c r="BJ6" s="33"/>
-      <c r="BK6" s="33"/>
-      <c r="BL6" s="33"/>
-      <c r="BM6" s="33"/>
-      <c r="BN6" s="33"/>
-    </row>
-    <row r="7" spans="1:66" ht="84.95" customHeight="1">
-      <c r="B7" s="26">
-        <v>3</v>
-      </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31"/>
-      <c r="T7" s="31"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="31"/>
-      <c r="X7" s="31"/>
-      <c r="Y7" s="31"/>
-      <c r="Z7" s="31"/>
-      <c r="AA7" s="31"/>
-      <c r="AB7" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC7" s="31"/>
-      <c r="AD7" s="31"/>
-      <c r="AE7" s="31"/>
-      <c r="AF7" s="31"/>
-      <c r="AG7" s="31"/>
-      <c r="AH7" s="31"/>
-      <c r="AI7" s="31"/>
-      <c r="AJ7" s="31"/>
-      <c r="AK7" s="31"/>
-      <c r="AL7" s="31"/>
-      <c r="AM7" s="31"/>
-      <c r="AN7" s="31"/>
-      <c r="AO7" s="31"/>
-      <c r="AP7" s="31"/>
-      <c r="AQ7" s="31"/>
-      <c r="AR7" s="31"/>
-      <c r="AS7" s="31"/>
-      <c r="AT7" s="31"/>
-      <c r="AU7" s="31"/>
-      <c r="AV7" s="31"/>
-      <c r="AW7" s="31"/>
-      <c r="AX7" s="31"/>
-      <c r="AY7" s="31"/>
-      <c r="AZ7" s="31"/>
-      <c r="BA7" s="31"/>
-      <c r="BB7" s="31"/>
-      <c r="BC7" s="32"/>
-      <c r="BD7" s="32"/>
-      <c r="BE7" s="32"/>
-      <c r="BF7" s="32"/>
-      <c r="BG7" s="32"/>
-      <c r="BH7" s="33"/>
-      <c r="BI7" s="33"/>
-      <c r="BJ7" s="33"/>
-      <c r="BK7" s="33"/>
-      <c r="BL7" s="33"/>
-      <c r="BM7" s="33"/>
-      <c r="BN7" s="33"/>
-    </row>
-    <row r="8" spans="1:66" ht="84.95" customHeight="1">
-      <c r="B8" s="26">
-        <v>4</v>
-      </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="31"/>
-      <c r="T8" s="31"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="31"/>
-      <c r="W8" s="31"/>
-      <c r="X8" s="31"/>
-      <c r="Y8" s="31"/>
-      <c r="Z8" s="31"/>
-      <c r="AA8" s="31"/>
-      <c r="AB8" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="AC8" s="31"/>
-      <c r="AD8" s="31"/>
-      <c r="AE8" s="31"/>
-      <c r="AF8" s="31"/>
-      <c r="AG8" s="31"/>
-      <c r="AH8" s="31"/>
-      <c r="AI8" s="31"/>
-      <c r="AJ8" s="31"/>
-      <c r="AK8" s="31"/>
-      <c r="AL8" s="31"/>
-      <c r="AM8" s="31"/>
-      <c r="AN8" s="31"/>
-      <c r="AO8" s="31"/>
-      <c r="AP8" s="31"/>
-      <c r="AQ8" s="31"/>
-      <c r="AR8" s="31"/>
-      <c r="AS8" s="31"/>
-      <c r="AT8" s="31"/>
-      <c r="AU8" s="31"/>
-      <c r="AV8" s="31"/>
-      <c r="AW8" s="31"/>
-      <c r="AX8" s="31"/>
-      <c r="AY8" s="31"/>
-      <c r="AZ8" s="31"/>
-      <c r="BA8" s="31"/>
-      <c r="BB8" s="31"/>
-      <c r="BC8" s="32"/>
-      <c r="BD8" s="32"/>
-      <c r="BE8" s="32"/>
-      <c r="BF8" s="32"/>
-      <c r="BG8" s="32"/>
-      <c r="BH8" s="33"/>
-      <c r="BI8" s="33"/>
-      <c r="BJ8" s="33"/>
-      <c r="BK8" s="33"/>
-      <c r="BL8" s="33"/>
-      <c r="BM8" s="33"/>
-      <c r="BN8" s="33"/>
-    </row>
-    <row r="9" spans="1:66" ht="84.95" customHeight="1">
-      <c r="B9" s="26">
-        <v>5</v>
-      </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="31"/>
-      <c r="T9" s="31"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="31"/>
-      <c r="W9" s="31"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="31"/>
-      <c r="Z9" s="31"/>
-      <c r="AA9" s="31"/>
-      <c r="AB9" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC9" s="31"/>
-      <c r="AD9" s="31"/>
-      <c r="AE9" s="31"/>
-      <c r="AF9" s="31"/>
-      <c r="AG9" s="31"/>
-      <c r="AH9" s="31"/>
-      <c r="AI9" s="31"/>
-      <c r="AJ9" s="31"/>
-      <c r="AK9" s="31"/>
-      <c r="AL9" s="31"/>
-      <c r="AM9" s="31"/>
-      <c r="AN9" s="31"/>
-      <c r="AO9" s="31"/>
-      <c r="AP9" s="31"/>
-      <c r="AQ9" s="31"/>
-      <c r="AR9" s="31"/>
-      <c r="AS9" s="31"/>
-      <c r="AT9" s="31"/>
-      <c r="AU9" s="31"/>
-      <c r="AV9" s="31"/>
-      <c r="AW9" s="31"/>
-      <c r="AX9" s="31"/>
-      <c r="AY9" s="31"/>
-      <c r="AZ9" s="31"/>
-      <c r="BA9" s="31"/>
-      <c r="BB9" s="31"/>
-      <c r="BC9" s="32"/>
-      <c r="BD9" s="32"/>
-      <c r="BE9" s="32"/>
-      <c r="BF9" s="32"/>
-      <c r="BG9" s="32"/>
-      <c r="BH9" s="33"/>
-      <c r="BI9" s="33"/>
-      <c r="BJ9" s="33"/>
-      <c r="BK9" s="33"/>
-      <c r="BL9" s="33"/>
-      <c r="BM9" s="33"/>
-      <c r="BN9" s="33"/>
-    </row>
-    <row r="10" spans="1:66" ht="45.95" customHeight="1">
-      <c r="B10" s="26">
-        <v>6</v>
-      </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="31"/>
-      <c r="Z10" s="31"/>
-      <c r="AA10" s="31"/>
-      <c r="AB10" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC10" s="31"/>
-      <c r="AD10" s="31"/>
-      <c r="AE10" s="31"/>
-      <c r="AF10" s="31"/>
-      <c r="AG10" s="31"/>
-      <c r="AH10" s="31"/>
-      <c r="AI10" s="31"/>
-      <c r="AJ10" s="31"/>
-      <c r="AK10" s="31"/>
-      <c r="AL10" s="31"/>
-      <c r="AM10" s="31"/>
-      <c r="AN10" s="31"/>
-      <c r="AO10" s="31"/>
-      <c r="AP10" s="31"/>
-      <c r="AQ10" s="31"/>
-      <c r="AR10" s="31"/>
-      <c r="AS10" s="31"/>
-      <c r="AT10" s="31"/>
-      <c r="AU10" s="31"/>
-      <c r="AV10" s="31"/>
-      <c r="AW10" s="31"/>
-      <c r="AX10" s="31"/>
-      <c r="AY10" s="31"/>
-      <c r="AZ10" s="31"/>
-      <c r="BA10" s="31"/>
-      <c r="BB10" s="31"/>
-      <c r="BC10" s="32"/>
-      <c r="BD10" s="32"/>
-      <c r="BE10" s="32"/>
-      <c r="BF10" s="32"/>
-      <c r="BG10" s="32"/>
-      <c r="BH10" s="33"/>
-      <c r="BI10" s="33"/>
-      <c r="BJ10" s="33"/>
-      <c r="BK10" s="33"/>
-      <c r="BL10" s="33"/>
-      <c r="BM10" s="33"/>
-      <c r="BN10" s="33"/>
-    </row>
-    <row r="11" spans="1:66" ht="76.900000000000006" customHeight="1">
-      <c r="B11" s="26">
-        <v>7</v>
-      </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="31"/>
-      <c r="T11" s="31"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="31"/>
-      <c r="W11" s="31"/>
-      <c r="X11" s="31"/>
-      <c r="Y11" s="31"/>
-      <c r="Z11" s="31"/>
-      <c r="AA11" s="31"/>
-      <c r="AB11" s="31" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="AC11" s="31"/>
       <c r="AD11" s="31"/>
@@ -13334,7 +13224,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="31" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
@@ -13359,7 +13249,7 @@
       <c r="Z5" s="31"/>
       <c r="AA5" s="31"/>
       <c r="AB5" s="31" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="AC5" s="31"/>
       <c r="AD5" s="31"/>
@@ -14240,7 +14130,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="31" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
@@ -14265,7 +14155,7 @@
       <c r="Z5" s="31"/>
       <c r="AA5" s="31"/>
       <c r="AB5" s="31" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="AC5" s="31"/>
       <c r="AD5" s="31"/>
@@ -15150,7 +15040,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="31" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
@@ -15223,7 +15113,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -15984,7 +15874,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="31" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
@@ -16057,7 +15947,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -16902,7 +16792,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="27" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -16975,7 +16865,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -17146,7 +17036,7 @@
       <c r="Z8" s="31"/>
       <c r="AA8" s="31"/>
       <c r="AB8" s="31" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="AC8" s="31"/>
       <c r="AD8" s="31"/>
@@ -17219,7 +17109,7 @@
       <c r="Z9" s="31"/>
       <c r="AA9" s="31"/>
       <c r="AB9" s="31" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="AC9" s="31"/>
       <c r="AD9" s="31"/>
@@ -17828,7 +17718,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="27" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -17901,7 +17791,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -18193,7 +18083,7 @@
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
       <c r="E10" s="31" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="31"/>
@@ -18218,7 +18108,7 @@
       <c r="Z10" s="31"/>
       <c r="AA10" s="31"/>
       <c r="AB10" s="31" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="AC10" s="31"/>
       <c r="AD10" s="31"/>
@@ -18754,7 +18644,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="27" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -18827,7 +18717,7 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="31" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -18973,7 +18863,7 @@
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
       <c r="E8" s="31" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
@@ -18998,7 +18888,7 @@
       <c r="Z8" s="31"/>
       <c r="AA8" s="31"/>
       <c r="AB8" s="31" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="AC8" s="31"/>
       <c r="AD8" s="31"/>
@@ -19046,7 +18936,7 @@
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
       <c r="E9" s="31" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
@@ -19071,7 +18961,7 @@
       <c r="Z9" s="31"/>
       <c r="AA9" s="31"/>
       <c r="AB9" s="31" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="AC9" s="31"/>
       <c r="AD9" s="31"/>
